--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128616808</v>
+        <v>128617384</v>
       </c>
       <c r="B13" t="n">
         <v>79083</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461433</v>
+        <v>461391</v>
       </c>
       <c r="R13" t="n">
-        <v>6794464</v>
+        <v>6794460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128617384</v>
+        <v>128617240</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461391</v>
+        <v>461390</v>
       </c>
       <c r="R14" t="n">
-        <v>6794460</v>
+        <v>6794474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128617240</v>
+        <v>128616808</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461390</v>
+        <v>461433</v>
       </c>
       <c r="R15" t="n">
-        <v>6794474</v>
+        <v>6794464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128616929</v>
+        <v>128618331</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461408</v>
+        <v>461338</v>
       </c>
       <c r="R23" t="n">
-        <v>6794478</v>
+        <v>6794474</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,6 +3028,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bild 7, garn i gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128616899</v>
+        <v>128616929</v>
       </c>
       <c r="B24" t="n">
         <v>79083</v>
@@ -3089,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461424</v>
+        <v>461408</v>
       </c>
       <c r="R24" t="n">
-        <v>6794468</v>
+        <v>6794478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,11 +3140,6 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bild 2, garn med kolbotten i bakgrund</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,7 +3166,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128616764</v>
+        <v>128616899</v>
       </c>
       <c r="B25" t="n">
         <v>79083</v>
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461428</v>
+        <v>461424</v>
       </c>
       <c r="R25" t="n">
-        <v>6794483</v>
+        <v>6794468</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,6 +3247,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bild 2, garn med kolbotten i bakgrund</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,7 +3278,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128618331</v>
+        <v>128616764</v>
       </c>
       <c r="B26" t="n">
         <v>79083</v>
@@ -3308,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461338</v>
+        <v>461428</v>
       </c>
       <c r="R26" t="n">
-        <v>6794474</v>
+        <v>6794483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,11 +3359,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bild 7, garn i gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4381,6 +4381,3046 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128631075</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79702</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>461195</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128631561</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>461165</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6794438</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128630639</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>461211</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6794451</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128630376</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>461270</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6794463</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128630436</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>461261</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6794439</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128630385</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>461270</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6794447</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128630434</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58115</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>461261</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6794439</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128631582</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>461168</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6794419</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128630448</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>461253</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128630471</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>461231</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6794440</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128630598</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>461214</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128630180</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91473</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>461229</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6794453</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2 bilder på tallticka och garnlav</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128630293</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>461252</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6794463</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Bild på stam, garn</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128630261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>461250</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6794456</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128630506</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>461231</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6794440</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Bild på stubbe</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128631047</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>461195</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Bild på raka med hackhål</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128630583</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58223</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>461214</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128630355</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>461268</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6794478</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128630139</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>461224</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6794454</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128631441</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>461172</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128630182</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>461240</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6794451</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128631672</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>461168</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6794419</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128631077</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>461195</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128630461</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>461246</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6794437</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128631081</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>461195</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6794436</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128631121</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>461199</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6794433</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Bild på raka</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128630337</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>461268</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6794470</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128631742</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>461193</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6794430</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128619475</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128618601</v>
       </c>
       <c r="B28" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>128616611</v>
       </c>
       <c r="B30" t="n">
-        <v>58115</v>
+        <v>58119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128619085</v>
       </c>
       <c r="B35" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4490,10 +4490,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128631561</v>
+        <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461165</v>
+        <v>461261</v>
       </c>
       <c r="R37" t="n">
-        <v>6794438</v>
+        <v>6794439</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128630436</v>
+        <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461261</v>
+        <v>461165</v>
       </c>
       <c r="R40" t="n">
-        <v>6794439</v>
+        <v>6794438</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128630434</v>
+        <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>58115</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,42 +5036,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461261</v>
+        <v>461168</v>
       </c>
       <c r="R42" t="n">
-        <v>6794439</v>
+        <v>6794419</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5137,10 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128631582</v>
+        <v>128630434</v>
       </c>
       <c r="B43" t="n">
-        <v>79083</v>
+        <v>58119</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5148,37 +5143,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461168</v>
+        <v>461261</v>
       </c>
       <c r="R43" t="n">
-        <v>6794419</v>
+        <v>6794439</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128630448</v>
+        <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461253</v>
+        <v>461231</v>
       </c>
       <c r="R44" t="n">
-        <v>6794436</v>
+        <v>6794440</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128630471</v>
+        <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461231</v>
+        <v>461253</v>
       </c>
       <c r="R45" t="n">
-        <v>6794440</v>
+        <v>6794436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5900,10 +5900,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128630506</v>
+        <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>79673</v>
+        <v>57686</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5911,34 +5911,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461231</v>
+        <v>461195</v>
       </c>
       <c r="R50" t="n">
-        <v>6794440</v>
+        <v>6794436</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5985,7 +5990,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Bild på stubbe</t>
+          <t>Bild på raka med hackhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6012,10 +6017,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128631047</v>
+        <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>57682</v>
+        <v>79677</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6023,39 +6028,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461195</v>
+        <v>461231</v>
       </c>
       <c r="R51" t="n">
-        <v>6794436</v>
+        <v>6794440</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Bild på raka med hackhål</t>
+          <t>Bild på stubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6129,50 +6129,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128630583</v>
+        <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>58223</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461214</v>
+        <v>461268</v>
       </c>
       <c r="R52" t="n">
-        <v>6794436</v>
+        <v>6794478</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6241,45 +6236,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128630355</v>
+        <v>128630583</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>58227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461268</v>
+        <v>461214</v>
       </c>
       <c r="R53" t="n">
-        <v>6794478</v>
+        <v>6794436</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128631081</v>
+        <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7097,32 +7097,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128631121</v>
+        <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461199</v>
+        <v>461268</v>
       </c>
       <c r="R61" t="n">
-        <v>6794433</v>
+        <v>6794470</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7178,11 +7178,6 @@
       <c r="AB61" t="inlineStr">
         <is>
           <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bild på raka</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7209,32 +7204,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128630337</v>
+        <v>128631121</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7244,10 +7239,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461268</v>
+        <v>461199</v>
       </c>
       <c r="R62" t="n">
-        <v>6794470</v>
+        <v>6794433</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7290,6 +7285,11 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Bild på raka</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7319,7 +7319,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128619475</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128618601</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>128616611</v>
       </c>
       <c r="B30" t="n">
-        <v>58119</v>
+        <v>58146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128619085</v>
       </c>
       <c r="B35" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128630434</v>
       </c>
       <c r="B43" t="n">
-        <v>58119</v>
+        <v>58146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5929,11 +5929,14 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
@@ -5990,7 +5993,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Bild på raka med hackhål</t>
+          <t>Bild på raka med hackhål samt miljöbild på angripen trädstam</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6020,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6132,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6239,7 +6242,7 @@
         <v>128630583</v>
       </c>
       <c r="B53" t="n">
-        <v>58227</v>
+        <v>58254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6565,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6672,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6886,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6993,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7100,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7319,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128619475</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128618601</v>
       </c>
       <c r="B28" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>128616611</v>
       </c>
       <c r="B30" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128619085</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128630434</v>
       </c>
       <c r="B43" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>128630583</v>
       </c>
       <c r="B53" t="n">
-        <v>58254</v>
+        <v>58258</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128619475</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>128618601</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>128616611</v>
       </c>
       <c r="B30" t="n">
-        <v>58150</v>
+        <v>58153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>128619085</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128630434</v>
       </c>
       <c r="B43" t="n">
-        <v>58150</v>
+        <v>58153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>128630583</v>
       </c>
       <c r="B53" t="n">
-        <v>58258</v>
+        <v>58261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79648</v>
+        <v>79653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128618541</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128619580</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128616195</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128619144</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128616622</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128617905</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128616632</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128619614</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>128619105</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>128617384</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>128617240</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>128616808</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>128619377</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>128619551</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>128619350</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>128617054</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>128618914</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128619622</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>128618331</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>128616929</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>128616899</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>128616764</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>128617663</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>128617937</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>128618585</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>128619122</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>128618994</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -4386,7 +4386,7 @@
         <v>128631075</v>
       </c>
       <c r="B36" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>128630436</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>128630639</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>128630376</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>128631574</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>128630385</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>128631582</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>128630434</v>
       </c>
       <c r="B43" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>128630471</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>128630448</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>128630598</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>128630293</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>128630261</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>128630355</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>128630583</v>
       </c>
       <c r="B53" t="n">
-        <v>58261</v>
+        <v>58263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>128630139</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>128631441</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>128630182</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>128631672</v>
       </c>
       <c r="B57" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>128631077</v>
       </c>
       <c r="B58" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>128630461</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>128631193</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>128630337</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>128631742</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>128631047</v>
       </c>
       <c r="B50" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>128630506</v>
       </c>
       <c r="B51" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 39480-2025 artfynd.xlsx
+++ b/artfynd/A 39480-2025 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>128630180</v>
       </c>
       <c r="B47" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
